--- a/outputs/Block5_Senate_Distribution.xlsx
+++ b/outputs/Block5_Senate_Distribution.xlsx
@@ -453,13 +453,13 @@
         <v>4</v>
       </c>
       <c r="B2">
-        <v>1.125104248703698</v>
+        <v>0.8003007397713651</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
       <c r="D2">
-        <v>0.08052834441621837</v>
+        <v>0.310958350932499</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -467,13 +467,13 @@
         <v>5</v>
       </c>
       <c r="B3">
-        <v>0.01190808928740122</v>
+        <v>0</v>
       </c>
       <c r="C3">
         <v>0</v>
       </c>
       <c r="D3">
-        <v>-0.009731676495348316</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -481,13 +481,13 @@
         <v>6</v>
       </c>
       <c r="B4">
-        <v>1.289478939532622</v>
+        <v>1.234402433809649</v>
       </c>
       <c r="C4">
         <v>1</v>
       </c>
       <c r="D4">
-        <v>-0.05380398015430821</v>
+        <v>-0.06279383028951013</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -495,13 +495,13 @@
         <v>7</v>
       </c>
       <c r="B5">
-        <v>0.8217382316493707</v>
+        <v>0.3293773794100608</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D5">
-        <v>0.3284488853529179</v>
+        <v>-0.2835868085528425</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -509,13 +509,13 @@
         <v>8</v>
       </c>
       <c r="B6">
-        <v>1.186511751275934</v>
+        <v>1.430889012604439</v>
       </c>
       <c r="C6">
         <v>1</v>
       </c>
       <c r="D6">
-        <v>0.03034414315627898</v>
+        <v>-0.2319645301829925</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -523,13 +523,13 @@
         <v>9</v>
       </c>
       <c r="B7">
-        <v>0.2977289224579263</v>
+        <v>0</v>
       </c>
       <c r="C7">
         <v>0</v>
       </c>
       <c r="D7">
-        <v>-0.2433137245397242</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -537,13 +537,13 @@
         <v>10</v>
       </c>
       <c r="B8">
-        <v>11.17487741647244</v>
+        <v>11.23658004704028</v>
       </c>
       <c r="C8">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D8">
-        <v>-0.1324719917360344</v>
+        <v>0.3255473089984537</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -551,13 +551,13 @@
         <v>11</v>
       </c>
       <c r="B9">
-        <v>0</v>
+        <v>0.06755162617559574</v>
       </c>
       <c r="C9">
         <v>0</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>-0.05816049090560802</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -565,13 +565,13 @@
         <v>12</v>
       </c>
       <c r="B10">
-        <v>0.851191504820574</v>
+        <v>0.6905082799680116</v>
       </c>
       <c r="C10">
         <v>1</v>
       </c>
       <c r="D10">
-        <v>0.01283822324504347</v>
+        <v>0.2119323948670038</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -579,13 +579,13 @@
         <v>13</v>
       </c>
       <c r="B11">
-        <v>0.4366083165842541</v>
+        <v>0.6558051063869967</v>
       </c>
       <c r="C11">
         <v>1</v>
       </c>
       <c r="D11">
-        <v>0.4936473882735054</v>
+        <v>0.2515386496910184</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -599,7 +599,7 @@
         <v>1</v>
       </c>
       <c r="D12">
-        <v>-0.1597411054555158</v>
+        <v>-0.141286249557361</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -607,13 +607,13 @@
         <v>15</v>
       </c>
       <c r="B13">
-        <v>1.081403752400103</v>
+        <v>0.9608490161719081</v>
       </c>
       <c r="C13">
         <v>1</v>
       </c>
       <c r="D13">
-        <v>-0.254148383252238</v>
+        <v>-0.09660377005771714</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -621,13 +621,13 @@
         <v>16</v>
       </c>
       <c r="B14">
-        <v>2.2065080011038</v>
+        <v>1.761149755943273</v>
       </c>
       <c r="C14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D14">
-        <v>0.4410219716034391</v>
+        <v>-0.009975999869360042</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -635,13 +635,13 @@
         <v>17</v>
       </c>
       <c r="B15">
-        <v>0.2302122475795285</v>
+        <v>0.2703407362038964</v>
       </c>
       <c r="C15">
         <v>0</v>
       </c>
       <c r="D15">
-        <v>-0.2669866064972812</v>
+        <v>-0.3085361649247209</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -649,13 +649,13 @@
         <v>18</v>
       </c>
       <c r="B16">
-        <v>12.72721886527684</v>
+        <v>13.28203815275881</v>
       </c>
       <c r="C16">
         <v>15</v>
       </c>
       <c r="D16">
-        <v>0.2397211238095416</v>
+        <v>-0.158607509839884</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -663,13 +663,13 @@
         <v>19</v>
       </c>
       <c r="B17">
-        <v>0.4366083165842541</v>
+        <v>0.6558051063869967</v>
       </c>
       <c r="C17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D17">
-        <v>-0.5063526117264946</v>
+        <v>0.2515386496910184</v>
       </c>
     </row>
   </sheetData>
